--- a/artfynd/A 12505-2026 artfynd.xlsx
+++ b/artfynd/A 12505-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6562113</v>
+        <v>432476</v>
       </c>
       <c r="B2" t="n">
-        <v>107457</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97776</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>231592</v>
+        <v>1590</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vesslefibbla</t>
+          <t>Dunmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hieracium chloromaurum</t>
+          <t>Trichocolea tomentella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Johanss.</t>
+          <t>(Ehrh.) Dumort.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Horn, Årtesmåla 975 m NV-ut, Ög</t>
+          <t>SO Grönlid (07F5j47), Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547249</v>
+        <v>547312</v>
       </c>
       <c r="R2" t="n">
-        <v>6423937</v>
+        <v>6423710</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2010-07-05</t>
+          <t>2001-12-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2010-07-05</t>
+          <t>2001-12-19</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>bestämd i fält till H. macradenium</t>
+          <t>070559471 / TRIC TOM / Tämligen allmän (2)  / OBJ.AREA:0 ha</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,31 +764,142 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>grusvägkant i skogsmark</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>Biologiska Museet, Lunds Universitet</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>AS10078</t>
+          <t>Källpåverkad mark /</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6562113</v>
+      </c>
+      <c r="B3" t="n">
+        <v>108754</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>231592</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vesslefibbla</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hieracium chloromaurum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Johanss.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Horn, Årtesmåla 975 m NV-ut, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>547249</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6423937</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Horn</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2010-07-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2010-07-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>bestämd i fält till H. macradenium</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>grusvägkant i skogsmark</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Biologiska Museet, Lunds Universitet</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>AS10078</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Anders Svenson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Anders Svenson, Tommy Nilsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12505-2026 artfynd.xlsx
+++ b/artfynd/A 12505-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/432476</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,8 +910,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6562113</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>